--- a/data/output/组合装数据0304.xlsx
+++ b/data/output/组合装数据0304.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,13 +453,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P100*2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>FZ68-0*2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>202混色</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P100</t>
+          <t>FZ68-0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -471,52 +475,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P200*3</t>
+          <t>MISSING*4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P200</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXIST1*2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EXIST1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MISSING*4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
